--- a/results/bemac/bemac_classB_Ru55_Rv77_SC/bler_vs_N.xlsx
+++ b/results/bemac/bemac_classB_Ru55_Rv77_SC/bler_vs_N.xlsx
@@ -480,7 +480,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BE-MAC — Class B, (Ru=0.55, Rv=0.77), SC (L=1), MC design</t>
+          <t>BE-MAC — Class B, (Ru=0.55, Rv=0.77), SC (L=1)</t>
         </is>
       </c>
     </row>
